--- a/284/food/kp2026.xlsx
+++ b/284/food/kp2026.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -125,26 +125,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -163,11 +143,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,22 +192,20 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -501,11 +499,11 @@
   <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.85546875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="4.28515625" customWidth="1" style="11" min="2" max="32"/>
+    <col width="7.85546875" customWidth="1" style="9" min="1" max="1"/>
+    <col width="4.28515625" customWidth="1" style="9" min="2" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="11">
+    <row r="1" ht="18.75" customHeight="1" s="9">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Школа</t>
@@ -516,14 +514,14 @@
           <t>МБОУ «СОШ "Терра Нова" им. Шарани Дудагова с. Мескер-юрт"</t>
         </is>
       </c>
-      <c r="C1" s="16" t="n"/>
-      <c r="D1" s="16" t="n"/>
-      <c r="E1" s="16" t="n"/>
-      <c r="F1" s="16" t="n"/>
-      <c r="G1" s="16" t="n"/>
-      <c r="H1" s="16" t="n"/>
-      <c r="I1" s="16" t="n"/>
-      <c r="J1" s="17" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="13" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="2" t="inlineStr">
         <is>
@@ -551,12 +549,12 @@
           <t>Год</t>
         </is>
       </c>
-      <c r="AD1" s="15" t="inlineStr">
+      <c r="AD1" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AE1" s="17" t="n"/>
+      <c r="AE1" s="13" t="n"/>
       <c r="AF1" s="1" t="n"/>
     </row>
     <row r="2">
@@ -740,53 +738,53 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" s="13" t="n">
+      <c r="M4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="13" t="n">
+      <c r="Q4" s="11" t="n">
         <v>5</v>
       </c>
       <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n"/>
-      <c r="T4" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="V4" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="T4" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="11" t="n">
         <v>10</v>
       </c>
       <c r="Y4" s="5" t="n"/>
       <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD4" s="13" t="n">
+      <c r="AA4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AE4" s="13" t="n">
+      <c r="AE4" s="11" t="n">
         <v>5</v>
       </c>
       <c r="AF4" s="5" t="n"/>
@@ -798,70 +796,62 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="13" t="n">
+      <c r="C5" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>10</v>
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="13" t="n">
+      <c r="J5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="13" t="n">
+      <c r="N5" s="11" t="n">
         <v>5</v>
       </c>
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="S5" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" s="13" t="n">
+      <c r="Q5" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" s="11" t="n">
         <v>10</v>
       </c>
       <c r="V5" s="5" t="n"/>
       <c r="W5" s="5" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" s="13" t="n">
-        <v>5</v>
-      </c>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
       <c r="AC5" s="5" t="n"/>
       <c r="AD5" s="6" t="n"/>
       <c r="AE5" s="6" t="n"/>
@@ -874,74 +864,80 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="C6" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>10</v>
       </c>
       <c r="H6" s="5" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" s="13" t="n">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="13" t="n">
+      <c r="N6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="O6" s="5" t="n"/>
       <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="S6" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U6" s="13" t="n">
+      <c r="Q6" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U6" s="11" t="n">
         <v>10</v>
       </c>
       <c r="V6" s="5" t="n"/>
       <c r="W6" s="5" t="n"/>
-      <c r="X6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="13" t="n">
+      <c r="X6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AB6" s="13" t="n">
+      <c r="AB6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="AC6" s="5" t="n"/>
       <c r="AD6" s="5" t="n"/>
-      <c r="AE6" s="7" t="n"/>
-      <c r="AF6" s="7" t="n"/>
+      <c r="AE6" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -949,72 +945,68 @@
           <t>апрель</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="B7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" s="13" t="n">
+      <c r="G7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="11" t="n">
         <v>10</v>
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="n"/>
-      <c r="N7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" s="13" t="n">
-        <v>5</v>
-      </c>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
       <c r="S7" s="5" t="n"/>
       <c r="T7" s="5" t="n"/>
-      <c r="U7" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="X7" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y7" s="13" t="n">
+      <c r="U7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="X7" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="11" t="n">
         <v>10</v>
       </c>
       <c r="Z7" s="5" t="n"/>
       <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE7" s="13" t="n">
+      <c r="AB7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="11" t="n">
         <v>4</v>
       </c>
       <c r="AF7" s="6" t="n"/>
@@ -1028,59 +1020,59 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" s="13" t="n">
+      <c r="E8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" s="13" t="n">
+      <c r="M8" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
-      <c r="S8" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T8" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" s="13" t="n">
+      <c r="S8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="X8" s="5" t="n"/>
       <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA8" s="13" t="n">
+      <c r="Z8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="11" t="n">
         <v>7</v>
       </c>
       <c r="AB8" s="7" t="n"/>
@@ -1133,78 +1125,78 @@
           <t>сентябрь</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="B10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="13" t="n">
+      <c r="H10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <v>10</v>
       </c>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
-      <c r="O10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" s="13" t="n">
+      <c r="O10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="S10" s="13" t="n">
+      <c r="S10" s="11" t="n">
         <v>5</v>
       </c>
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="5" t="n"/>
-      <c r="V10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" s="13" t="n">
+      <c r="V10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="11" t="n">
         <v>10</v>
       </c>
       <c r="AA10" s="5" t="n"/>
       <c r="AB10" s="5" t="n"/>
-      <c r="AC10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" s="13" t="n">
+      <c r="AC10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="11" t="n">
         <v>3</v>
       </c>
       <c r="AF10" s="6" t="n"/>
@@ -1215,81 +1207,81 @@
           <t>октябрь</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" s="13" t="n">
+      <c r="F11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="13" t="n">
+      <c r="M11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" s="13" t="n">
+      <c r="Q11" s="11" t="n">
         <v>5</v>
       </c>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="U11" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="X11" s="13" t="n">
+      <c r="T11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="X11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="Y11" s="5" t="n"/>
       <c r="Z11" s="5" t="n"/>
-      <c r="AA11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD11" s="13" t="n">
+      <c r="AA11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AE11" s="13" t="n">
+      <c r="AE11" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="AF11" s="12" t="n"/>
+      <c r="AF11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1297,7 +1289,7 @@
           <t>ноябрь</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
+      <c r="B12" s="10" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
@@ -1305,58 +1297,58 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
-      <c r="J12" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="N12" s="13" t="n">
+      <c r="J12" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" s="11" t="n">
         <v>10</v>
       </c>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" s="13" t="n">
+      <c r="Q12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="U12" s="13" t="n">
+      <c r="U12" s="11" t="n">
         <v>5</v>
       </c>
       <c r="V12" s="5" t="n"/>
       <c r="W12" s="5" t="n"/>
-      <c r="X12" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y12" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB12" s="13" t="n">
+      <c r="X12" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="11" t="n">
         <v>10</v>
       </c>
       <c r="AC12" s="5" t="n"/>
       <c r="AD12" s="5" t="n"/>
-      <c r="AE12" s="13" t="n">
+      <c r="AE12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="AF12" s="6" t="n"/>
@@ -1367,78 +1359,78 @@
           <t>декабрь</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="13" t="n">
+      <c r="B13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="L13" s="13" t="n">
+      <c r="H13" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
-      <c r="O13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" s="13" t="n">
+      <c r="O13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="S13" s="13" t="n">
+      <c r="S13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
-      <c r="V13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="W13" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y13" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z13" s="13" t="n">
+      <c r="V13" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="AA13" s="5" t="n"/>
       <c r="AB13" s="5" t="n"/>
-      <c r="AC13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE13" s="13" t="n">
+      <c r="AC13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="11" t="n">
         <v>3</v>
       </c>
       <c r="AF13" s="4" t="n"/>
